--- a/BEU_Results_Report.xlsx
+++ b/BEU_Results_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,60 +466,65 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>100602 : Computer Networks</t>
+          <t>100102 : Engineering Mathematics-I</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>105601 : Compiler Design</t>
+          <t>100110 : Engineering Physics</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>105602 : Machine Learning</t>
+          <t>100111 : Programming for Problem Solving</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>105604 : Graph Theory</t>
+          <t>100113 : IT Workshop</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>105614 : Web and Internet Technology</t>
+          <t>100114 : Basic Electronics Engineering</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>100602P : Computer Networks</t>
+          <t>100110P : Engineering Physics Lab</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>100604P : MOOCs / SWAYAM / NPTEL Courses - 2</t>
+          <t>100111P : Programming for Problem Solving Lab</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>105601P : Compiler Design</t>
+          <t>100113P : IT Workshop Lab</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>105620P : Python Programming</t>
+          <t>100114P : Basic Electronics Engineering Lab</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>100115P : Swachha Bharat Mission</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>SGPA</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>CGPA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
@@ -527,21 +532,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22105134001</v>
+        <v>24155134001</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NIKITA KUMARI</t>
+          <t>NANDANI KUMARI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KAILASH RAJAK</t>
+          <t>SHIVANAND YADAV</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RANJANA DEVI</t>
+          <t>SHOBHA DEVI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -551,70 +556,75 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>6.63</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
+        <is>
+          <t>6.90</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -622,21 +632,21 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>22105134002</v>
+        <v>24155134002</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADARSH KUMAR</t>
+          <t>ASTIK BHARTI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SANJAY KUMAR SAH</t>
+          <t>SANJAY KUMAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BABITA DEVI</t>
+          <t>SARITA KUMARI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -646,92 +656,97 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>FAIL:100102</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>22105134003</v>
+        <v>24155134003</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HRITHIK RAUSHAN</t>
+          <t>KISHLAY KUMAR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAMIR KUMAR</t>
+          <t>SANJAY KUMAR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RUPA DEVI</t>
+          <t>NUTAN KUMARI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -741,70 +756,75 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>51</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
+        <is>
+          <t>8.65</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -812,21 +832,21 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22105134004</v>
+        <v>24155134004</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SARWAJEET KUMAR</t>
+          <t>SATYAJEET KUMAR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARVIND KUMAR SINGH</t>
+          <t>RAM PRABHANJAN CHOUDHARY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GEETA DEVI</t>
+          <t>MAMTA DEVI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -836,37 +856,37 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -876,30 +896,35 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -907,21 +932,21 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>22105134005</v>
+        <v>24155134005</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SHUBHAM KUMAR</t>
+          <t>VIMAL KUMAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SUNIL KUMAR MISHRA</t>
+          <t>CHANDRIKA PRASAD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RANJANA DEVI</t>
+          <t>KIRAN KUMARI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -931,92 +956,97 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>51</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>FAIL:100102</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>22105134006</v>
+        <v>24155134006</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ABHINAV KUMAR</t>
+          <t>YUVRAJ SUNDARAM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MUKESH KUMAR</t>
+          <t>RAVINDRA KUMAR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BEENA DEVI</t>
+          <t>REENA KUMARI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1026,70 +1056,75 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>27</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1097,21 +1132,21 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>22105134007</v>
+        <v>24155134007</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UJWAL SANGAM</t>
+          <t>RITIK KUMAR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DHANANJAY KUMAR</t>
+          <t>RAJNARAYAN SINGH</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NUTAN KUMARI</t>
+          <t>SHIMAL DEVI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1121,92 +1156,97 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>FAIL:105602</t>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>FAIL:100110</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>22105134008</v>
+        <v>24155134008</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RISHU RAJ</t>
+          <t>RAKESH KUMAR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SURENDRA PRASAD</t>
+          <t>PURUSHOTTAM SAH</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RENU DEVI</t>
+          <t>SAVITA DEVI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1216,70 +1256,75 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>39</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
+        <is>
+          <t>7.30</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1287,21 +1332,21 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>22105134009</v>
+        <v>24155134009</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RAHUL KUMAR</t>
+          <t>YUVRAJ ARYAN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SANJAY KUMAR CHAUDHARY</t>
+          <t>RAMAN KUMAR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PUNAM DEVI</t>
+          <t>SIMA GUPTA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1311,37 +1356,37 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1351,52 +1396,57 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>FAIL:100102</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22105134010</v>
+        <v>24155134010</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VISHAL KUMAR</t>
+          <t>ANURAG KUMAR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MANOJ KUMAR</t>
+          <t>DHARMENDRA SAH</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MADHU DEVI</t>
+          <t>CHANDA DEVI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1406,12 +1456,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1421,7 +1471,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1431,63 +1481,72 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>FAIL:100602,105601</t>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>FAIL:100102,100110</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>22105134011</v>
+        <v>24155134011</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PRIYA KUMARI</t>
+          <t>JAINEE KUMARI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MAHENDRA KUMAR GUPTA</t>
+          <t>RAM NARESH JHA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAXMINA DEVI</t>
+          <t>RANI DEVI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1497,70 +1556,75 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>52</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1568,21 +1632,21 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>22105134012</v>
+        <v>24155134012</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAKSHI SRI</t>
+          <t>PRANJAL VERMA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SHALENDRA KUMAR</t>
+          <t>KEDAR PRASAD VERMA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SUMAN BHARTI</t>
+          <t>PRITY VERMA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1592,70 +1656,75 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
+        <is>
+          <t>6.90</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1663,21 +1732,21 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22105134013</v>
+        <v>24155134013</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PREM KUMAR</t>
+          <t>AYUSHI RANI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PAPPU PRASAD</t>
+          <t>UPENDRA KUMAR SHARMA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DEEPAK DEVI</t>
+          <t>ASHA KUMARI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1687,70 +1756,75 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
+        <is>
+          <t>7.55</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1758,21 +1832,21 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>22105134014</v>
+        <v>24155134014</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MD ADNAN AKHTER</t>
+          <t>ANJALI SINGH TOMAR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MD KAMIL AKHTER</t>
+          <t>TRIBHUWAN KUMAR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SHAMA PERWEEN</t>
+          <t>MADHU SINGH</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1782,17 +1856,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1802,50 +1876,55 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
+        <is>
+          <t>7.30</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1853,21 +1932,21 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>22105134015</v>
+        <v>24155134015</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RAJ KUMAR</t>
+          <t>PRIYANSHU KUMARI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JAIMANGAL CHOUDHARI</t>
+          <t>SANJAY KUMAR YADAV</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>REKHA DEVI</t>
+          <t>GUDDI DEVI</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1877,92 +1956,97 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>FAIL:100602,105602,105604</t>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>22105134016</v>
+        <v>24155134016</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ADITYA DHANRAJ</t>
+          <t>SURAJ KUMAR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SHAMBHU SHARAN ROY</t>
+          <t>BINOD KUMAR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RENU SINHA</t>
+          <t>VEENA DEVI</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1972,70 +2056,75 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
+        <is>
+          <t>6.95</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2043,21 +2132,21 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>22105134017</v>
+        <v>24155134017</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SHUBHAM KUMAR</t>
+          <t>ADARSH KUMAR MISHRA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DHARMENDRA KUMAR</t>
+          <t>SANJAY KUMAR MISHRA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BABY DEVI</t>
+          <t>NEELAM DEVI</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2067,70 +2156,75 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>7.44</t>
-        </is>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
+        <is>
+          <t>6.70</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2138,21 +2232,21 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22105134018</v>
+        <v>24155134018</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RAHUL KUMAR</t>
+          <t>DOLLY KUMARI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CHANDRA DAS</t>
+          <t>DINENDRA KUMAR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JHALIA DEVI</t>
+          <t>ASHA DEVI</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2162,92 +2256,97 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>49</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>FAIL:100602,105601</t>
+          <t>7.70</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22105134019</v>
+        <v>24155134019</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RAJNISH KUMAR</t>
+          <t>PRIYAM KUMARI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MANTU MANDAL</t>
+          <t>VINOD KUMAR PAL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CHANDRAKANTI DEVI</t>
+          <t>MEENA KUMARI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2257,88 +2356,97 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>FAIL:100602</t>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22105134020</v>
+        <v>24155134020</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ABHISHEK KUMAR</t>
+          <t>SURABHI KUMARI SINGH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KRITLAL MANDAL</t>
+          <t>RAGHAW SINGH</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KANCHAN SUDHA</t>
+          <t>GUDDI DEVI SINGH</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2348,70 +2456,75 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
+        <is>
+          <t>7.65</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2419,21 +2532,21 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22105134021</v>
+        <v>24155134021</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MD DANISH</t>
+          <t>PIYUSH KUMAR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MD BAHAUL HAQUE</t>
+          <t>MAHESH RAJAK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>REHANA KHATOON</t>
+          <t>SEEMA DEVI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2443,70 +2556,75 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2514,21 +2632,21 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22105134022</v>
+        <v>24155134022</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MD ANWAR HUSSAIN</t>
+          <t>BALVEER KUMAR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MD MOJAHID HUSSAIN</t>
+          <t>RANJAY KUMAR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NASRIN AKTHER</t>
+          <t>KUNDAN DEVI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2538,70 +2656,75 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
+        <is>
+          <t>7.60</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2609,21 +2732,21 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22105134023</v>
+        <v>24155134023</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KESHAV KUMAR</t>
+          <t>ARADHYA KUMARI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MITHILESH KUMAR</t>
+          <t>ASHOK KUMAR SINGH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JYOTI DEVI</t>
+          <t>MANJU DEVI</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2633,92 +2756,97 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>5.80</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>FAIL:100110</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>22105134024</v>
+        <v>24155134024</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAURABH KUMAR</t>
+          <t>SAURAV KUMAR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DHARMENDRA SINGH</t>
+          <t>AMAR YADAV</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ANITA VERMA</t>
+          <t>SWEETI DEVI</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2728,37 +2856,37 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>43</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2768,7 +2896,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2778,20 +2906,25 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
+        <is>
+          <t>7.30</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2799,21 +2932,21 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22105134025</v>
+        <v>24155134025</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PRATIK KUMAR</t>
+          <t>ANSHU PRIYA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PREM KUMAR PRIANK</t>
+          <t>BIPIN KUMAR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>RIBHA DEVI</t>
+          <t>RAJNANDANI DEVI</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2823,70 +2956,75 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>39</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
+        <is>
+          <t>7.40</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2894,21 +3032,21 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>23105134901</v>
+        <v>24155134026</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SUNNY KUMAR</t>
+          <t>SUPRIYA KUMARI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BRAJ KISHORE PRASAD</t>
+          <t>AHSOK KUMAR SINGH</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SANJU DEVI</t>
+          <t>PUSHPA DEVI</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2918,92 +3056,97 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>FAIL:100102</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>23105134902</v>
+        <v>24155134027</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MUSKAN ARYA</t>
+          <t>PUSHPANJALI KUMARI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GOPAL ARYA</t>
+          <t>INDAL KUMAR SINGH</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>RINA DEVI</t>
+          <t>SARITA DEVI</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3013,70 +3156,75 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>34</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
+        <is>
+          <t>6.35</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3084,21 +3232,21 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>23105134904</v>
+        <v>24155134028</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SALONI KUMARI</t>
+          <t>ASHISH KUMAR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RAMPATI GUPTA</t>
+          <t>DEEPAK PRASAD</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KIRAN DEVI</t>
+          <t>PRATIMA DEVI</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3108,92 +3256,97 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>38</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>FAIL:100110</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>23105134905</v>
+        <v>24155134029</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BHAVYA KUMARI</t>
+          <t>SHIWANI KUMARI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SANJEEV KUMAR SINGH</t>
+          <t>ASHOK KUMAR MAHTO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MANISHA DEVI</t>
+          <t>KARUNA DEVI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3203,70 +3356,75 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>49</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3274,21 +3432,21 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>23105134906</v>
+        <v>24155134030</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PRIYANSHU KUMARI</t>
+          <t>KRITIKA MEHTA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SHOBHNATH PRASAD</t>
+          <t>RAVI RANJAN KUMAR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SANDHYA DEVI</t>
+          <t>SHWETA SINGH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3298,92 +3456,97 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>28</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>FAIL:100102</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>23105134907</v>
+        <v>24155134031</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ROHIT RAJ SINHA</t>
+          <t>ANANT PRAKASH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SANJAY SINHA</t>
+          <t>MUKESH KUMAR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RINA SINHA</t>
+          <t>PUNAM DEVI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3393,37 +3556,37 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>29</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3433,52 +3596,57 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>FAIL:100102,100110</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>23105134908</v>
+        <v>24155134032</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ANUBANDHAN KUMAR</t>
+          <t>SIMRAN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MAHADEV MANDAL</t>
+          <t>LATE SANJEEV KUMAR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CHANDANI DEVI</t>
+          <t>SUGEETA KUMARI</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3488,92 +3656,97 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>5.55</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>FAIL:100102</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>23105134909</v>
+        <v>24155134033</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ANAMIKA SAHGAL</t>
+          <t>MONIKA KUMARI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ARUN KUMAR</t>
+          <t>KRISHAN KISHOR KUMAR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RINKU KUMARI DEVI</t>
+          <t>KRISHNA KUMARI</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3583,70 +3756,75 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3654,21 +3832,21 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>23105134910</v>
+        <v>24155134034</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SATYAM KUMAR</t>
+          <t>MD ABUJAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RAJEEV RANJAN PANDEY</t>
+          <t>MD MAZID</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SUDHA DEVI</t>
+          <t>ANISHA KHATOON</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3678,72 +3856,2177 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE &amp; ENGINEERING</t>
+          <t>Computer Science and Engineering (Internet of Things)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>FAIL:100110,100114</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>24155134035</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>VIVEK KUMAR</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MANJU DEVI</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>FAIL:100110</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>24155134036</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PRINCE KUMAR</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PRAMOD RAY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>USHA DEVI</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>FAIL:100114</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>24155134037</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NIRAJ KUMAR PASWAN</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR PASWAN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MIRA DEVI</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>7.90</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>7.90</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24155134038</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ANSHULAL</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AJIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PUSHPA DEVI</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>24155134039</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ANIKET RANJAN</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>GEETA KUMARI</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>FAIL:100102</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>24155134040</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ANURAG KUMAR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PAWAN KUMAR PANDIT</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BINDA DEVI</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>24155134041</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ABHISHEK KUMAR</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SUJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RANJU DEVI</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>6.95</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>6.95</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>24155134042</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ABHISHEK ANAND</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR ANAL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MAYA DEVI</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>7.70</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>7.70</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>24155134043</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ANURAG KESHAV</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>KISHORI PRASAD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ANJANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>24155134044</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AMAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SURYADEV PANDIT</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>6.70</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>6.70</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>24155134045</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HIMANSHU KUMAR</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SUMAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BEVI DEVI</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>24155134046</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DIWAKAR KUMAR</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>JAI NATH MAHTO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SUNITA DEVI</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>6.60</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>6.60</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>24155134047</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>VIKASH KUMAR</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>RAMASHRAY YADAV</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MANTO DEVI</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>24155134049</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GANESH KUMAR</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DILEEP CHAUDHARY</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>RINA DEVI</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>6.55</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>6.55</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>24155134050</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ANSH KUMAR KUSHWAHA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MANOJ MAHTO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RUCHI DEVI</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>FAIL:100102,100110,100111</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>24155134051</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PRAKRIT SASHAKT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CHANDRA PRAKASH DHIRAJ</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SINDHU KUMARI</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>FAIL:100102,100110</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>24155134052</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AMARJEET YADAV</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>RAM EKBAL YADAV</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ANJU DEVI</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>FAIL:100110</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>24155134053</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SATYAM SHANDILIYA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR JHA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SUCHITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>6.55</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>6.55</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>24155134054</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SHYAM YADAV</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BHOLA YADAV</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PUNITA DEVI</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>7.45</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>7.45</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>24155134055</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>DHARMPRIYA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TUSI DEVI</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>8.30</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>8.30</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>24155134056</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>KUNAL KUMAR</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR GUPTA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>RENU DEVI</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>GOVERNMENT ENGINEERING COLLEGE, BANKA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering (Internet of Things)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>7.42</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>FAIL:100102</t>
         </is>
       </c>
     </row>
